--- a/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_49.xlsx
+++ b/model/Outputs/11. Interest rate/30/Output Files/0.3/Output_6_49.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3588970.658388211</v>
+        <v>3581993.273696084</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>9956801.353979917</v>
+        <v>9956801.353979919</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9956801.353979917</v>
+        <v>9956801.353979919</v>
       </c>
     </row>
     <row r="9">
@@ -672,10 +672,10 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>176.4246500889419</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -702,7 +702,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>18.33383170272989</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -739,22 +739,22 @@
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>67.51997340159429</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>192.3498461705184</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -793,7 +793,7 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
-        <v>414.5106671915202</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -909,7 +909,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>176.4246500889419</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -960,7 +960,7 @@
         <v>192.2818334606677</v>
       </c>
       <c r="Y5" t="n">
-        <v>111.3174326828064</v>
+        <v>279.7324240682209</v>
       </c>
     </row>
     <row r="6">
@@ -976,7 +976,7 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>143.3592314182239</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -985,7 +985,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -1015,7 +1015,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R6" t="n">
         <v>147.2737972923793</v>
@@ -1024,7 +1024,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>5.357765217513816</v>
+        <v>405.3577652175138</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
@@ -1033,7 +1033,7 @@
         <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>421</v>
+        <v>317.0195022027718</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1131,7 +1131,7 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C8" t="n">
-        <v>49.47457824299391</v>
+        <v>217.8895696284084</v>
       </c>
       <c r="D8" t="n">
         <v>10.33915573984979</v>
@@ -1146,7 +1146,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>176.4246500889419</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1216,7 +1216,7 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>192.3498461705184</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -1225,7 +1225,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H9" t="n">
-        <v>192.3498461705185</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -1386,7 +1386,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I11" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T11" t="n">
         <v>236.6755817285639</v>
@@ -1444,13 +1444,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C12" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>62.67776252544251</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1459,10 +1459,10 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>86.93822665041519</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1623,7 +1623,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1650,7 +1650,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>144.8481678023229</v>
@@ -1690,13 +1690,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>70.00566530352994</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -1729,10 +1729,10 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S15" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T15" t="n">
         <v>55.35776521751382</v>
@@ -1851,7 +1851,7 @@
         <v>54.36328960686865</v>
       </c>
       <c r="F17" t="n">
-        <v>58.85502009342638</v>
+        <v>54.88962870801186</v>
       </c>
       <c r="G17" t="n">
         <v>53.75737228701621</v>
@@ -1860,7 +1860,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1966,7 +1966,7 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S18" t="n">
         <v>116.5639999646113</v>
@@ -1975,10 +1975,10 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U18" t="n">
-        <v>50.21035976018675</v>
+        <v>112.8881222856292</v>
       </c>
       <c r="V18" t="n">
-        <v>414.5106671915202</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W18" t="n">
         <v>82.37314290982852</v>
@@ -1987,7 +1987,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y18" t="n">
-        <v>112.0691552915768</v>
+        <v>49.39139276613435</v>
       </c>
     </row>
     <row r="19">
@@ -2082,7 +2082,7 @@
         <v>99.47457824299391</v>
       </c>
       <c r="D20" t="n">
-        <v>64.30454712526431</v>
+        <v>60.33915573984979</v>
       </c>
       <c r="E20" t="n">
         <v>54.36328960686865</v>
@@ -2097,7 +2097,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>197.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S21" t="n">
-        <v>116.5639999646113</v>
+        <v>179.2417624900537</v>
       </c>
       <c r="T21" t="n">
         <v>55.35776521751382</v>
@@ -2221,7 +2221,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X21" t="n">
-        <v>150.372414784409</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y21" t="n">
         <v>49.39139276613435</v>
@@ -2361,7 +2361,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S23" t="n">
         <v>144.8481678023229</v>
@@ -2376,7 +2376,7 @@
         <v>279.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>292.3388673663621</v>
+        <v>288.3734759809475</v>
       </c>
       <c r="X23" t="n">
         <v>242.2818334606677</v>
@@ -2392,7 +2392,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>34.55655664632661</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
         <v>11.09991244551929</v>
@@ -2443,10 +2443,10 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S24" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T24" t="n">
-        <v>405.3577652175138</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U24" t="n">
         <v>50.21035976018675</v>
@@ -2458,7 +2458,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X24" t="n">
-        <v>69.86273944538755</v>
+        <v>132.54050197083</v>
       </c>
       <c r="Y24" t="n">
         <v>49.39139276613435</v>
@@ -2568,7 +2568,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H26" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>148.8135591877373</v>
+        <v>144.8481678023229</v>
       </c>
       <c r="T26" t="n">
         <v>236.6755817285639</v>
@@ -2629,13 +2629,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>99.2966322740666</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C27" t="n">
         <v>11.09991244551929</v>
       </c>
       <c r="D27" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -2650,7 +2650,7 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2686,7 +2686,7 @@
         <v>55.35776521751382</v>
       </c>
       <c r="U27" t="n">
-        <v>50.21035976018675</v>
+        <v>245.7617363942807</v>
       </c>
       <c r="V27" t="n">
         <v>64.51066719152016</v>
@@ -2872,22 +2872,22 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D30" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>64.74007562773993</v>
+        <v>0</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>195.551376634094</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -3030,7 +3030,7 @@
         <v>99.47457824299391</v>
       </c>
       <c r="D32" t="n">
-        <v>64.30454712526431</v>
+        <v>60.33915573984979</v>
       </c>
       <c r="E32" t="n">
         <v>54.36328960686865</v>
@@ -3042,7 +3042,7 @@
         <v>53.75737228701621</v>
       </c>
       <c r="H32" t="n">
-        <v>58.00965870352741</v>
+        <v>61.97505008894191</v>
       </c>
       <c r="I32" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3148,7 +3148,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
         <v>197.2737972923793</v>
@@ -3172,7 +3172,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y33" t="n">
-        <v>288.9898902010971</v>
+        <v>244.9427694002283</v>
       </c>
     </row>
     <row r="34">
@@ -3346,7 +3346,7 @@
         <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
@@ -3385,10 +3385,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
-        <v>197.2737972923793</v>
+        <v>219.7459088359936</v>
       </c>
       <c r="S36" t="n">
         <v>116.5639999646113</v>
@@ -3519,7 +3519,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3546,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>3.965391385414537</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>144.8481678023229</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3622,7 +3622,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>197.2737972923793</v>
@@ -3637,7 +3637,7 @@
         <v>50.21035976018675</v>
       </c>
       <c r="V39" t="n">
-        <v>127.1884297169627</v>
+        <v>64.51066719152016</v>
       </c>
       <c r="W39" t="n">
         <v>82.37314290982852</v>
@@ -3646,7 +3646,7 @@
         <v>69.86273944538755</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>71.86350430974859</v>
       </c>
     </row>
     <row r="40">
@@ -3823,7 +3823,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F42" t="n">
         <v>0</v>
@@ -3859,10 +3859,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>197.2737972923793</v>
+        <v>436.872294727342</v>
       </c>
       <c r="S42" t="n">
         <v>116.5639999646113</v>
@@ -3880,7 +3880,7 @@
         <v>82.37314290982852</v>
       </c>
       <c r="X42" t="n">
-        <v>139.8684047489175</v>
+        <v>69.86273944538755</v>
       </c>
       <c r="Y42" t="n">
         <v>49.39139276613435</v>
@@ -3993,7 +3993,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>3.965391385414508</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -4029,7 +4029,7 @@
         <v>236.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>303.1866879340253</v>
+        <v>299.2212965486107</v>
       </c>
       <c r="V44" t="n">
         <v>279.8510241668239</v>
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>384.5565566463266</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
         <v>11.09991244551929</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,16 +4096,16 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>197.2737972923793</v>
+        <v>219.7459088359936</v>
       </c>
       <c r="S45" t="n">
         <v>116.5639999646113</v>
       </c>
       <c r="T45" t="n">
-        <v>118.0355277429563</v>
+        <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
         <v>50.21035976018675</v>
@@ -4297,76 +4297,76 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>266.9273161322752</v>
+        <v>285.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>216.9529946747056</v>
+        <v>235.472016596655</v>
       </c>
       <c r="D2" t="n">
-        <v>206.5094030182917</v>
+        <v>225.028424940241</v>
       </c>
       <c r="E2" t="n">
-        <v>202.1020397790304</v>
+        <v>220.6210617009798</v>
       </c>
       <c r="F2" t="n">
-        <v>197.1630208820488</v>
+        <v>215.6820428039981</v>
       </c>
       <c r="G2" t="n">
-        <v>193.3676953396081</v>
+        <v>211.8867172615575</v>
       </c>
       <c r="H2" t="n">
-        <v>185.2771309926108</v>
+        <v>33.68</v>
       </c>
       <c r="I2" t="n">
         <v>33.68</v>
       </c>
       <c r="J2" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="K2" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="L2" t="n">
-        <v>33.68</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="M2" t="n">
-        <v>33.68</v>
+        <v>841.7791130376559</v>
       </c>
       <c r="N2" t="n">
-        <v>450.47</v>
+        <v>1258.569113037656</v>
       </c>
       <c r="O2" t="n">
-        <v>867.26</v>
+        <v>1675.359113037656</v>
       </c>
       <c r="P2" t="n">
-        <v>1284.05</v>
+        <v>1684</v>
       </c>
       <c r="Q2" t="n">
         <v>1684</v>
       </c>
       <c r="R2" t="n">
-        <v>1665.480978078051</v>
+        <v>1684</v>
       </c>
       <c r="S2" t="n">
-        <v>1569.674747974694</v>
+        <v>1588.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1381.113554309478</v>
+        <v>1399.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>1129.374870927043</v>
+        <v>1147.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>897.2021192433824</v>
+        <v>915.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>656.4208303737385</v>
+        <v>674.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>462.1967561710438</v>
+        <v>480.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>349.7549049762899</v>
+        <v>368.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4376,76 +4376,76 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>816.0891546748412</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="C3" t="n">
-        <v>816.0891546748412</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="D3" t="n">
-        <v>747.8871613398975</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="E3" t="n">
-        <v>747.8871613398975</v>
+        <v>705.7767456696004</v>
       </c>
       <c r="F3" t="n">
-        <v>747.8871613398975</v>
+        <v>362.7098342171994</v>
       </c>
       <c r="G3" t="n">
-        <v>747.8871613398975</v>
+        <v>33.68</v>
       </c>
       <c r="H3" t="n">
-        <v>747.8871613398975</v>
+        <v>33.68</v>
       </c>
       <c r="I3" t="n">
-        <v>528.5675796314646</v>
+        <v>33.68</v>
       </c>
       <c r="J3" t="n">
-        <v>652.5240998067635</v>
+        <v>157.636520175299</v>
       </c>
       <c r="K3" t="n">
-        <v>841.7169159011469</v>
+        <v>346.8293362696824</v>
       </c>
       <c r="L3" t="n">
-        <v>1113.067377496347</v>
+        <v>618.1797978648824</v>
       </c>
       <c r="M3" t="n">
-        <v>1199.147919239206</v>
+        <v>704.2603396077417</v>
       </c>
       <c r="N3" t="n">
-        <v>1332.428203846775</v>
+        <v>837.54062421531</v>
       </c>
       <c r="O3" t="n">
-        <v>1571.470655530493</v>
+        <v>1076.583075899029</v>
       </c>
       <c r="P3" t="n">
-        <v>1684</v>
+        <v>1189.112420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1509.172459504566</v>
+        <v>1189.112420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>1360.411048098122</v>
+        <v>1040.351008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>1293.174684497505</v>
+        <v>973.1146453614743</v>
       </c>
       <c r="T3" t="n">
-        <v>1287.76280043941</v>
+        <v>967.7027613033796</v>
       </c>
       <c r="U3" t="n">
-        <v>1287.550315833161</v>
+        <v>967.4902766971303</v>
       </c>
       <c r="V3" t="n">
-        <v>868.8526722053625</v>
+        <v>952.8330371097362</v>
       </c>
       <c r="W3" t="n">
-        <v>836.1525278520004</v>
+        <v>920.1328927563741</v>
       </c>
       <c r="X3" t="n">
-        <v>816.0891546748412</v>
+        <v>900.0695195792149</v>
       </c>
       <c r="Y3" t="n">
-        <v>816.0891546748412</v>
+        <v>900.0695195792149</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>731.0950004875772</v>
+        <v>815.8399956093144</v>
       </c>
       <c r="C4" t="n">
-        <v>731.0950004875772</v>
+        <v>815.8399956093144</v>
       </c>
       <c r="D4" t="n">
-        <v>787.8070597341388</v>
+        <v>929.1591397343145</v>
       </c>
       <c r="E4" t="n">
-        <v>905.6359639455518</v>
+        <v>986.838685501737</v>
       </c>
       <c r="F4" t="n">
-        <v>1029.996936537487</v>
+        <v>1111.199658093672</v>
       </c>
       <c r="G4" t="n">
-        <v>1183.403502424373</v>
+        <v>1264.606223980558</v>
       </c>
       <c r="H4" t="n">
-        <v>1183.403502424373</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="I4" t="n">
-        <v>1183.403502424373</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="J4" t="n">
-        <v>1544.487243076824</v>
+        <v>1434.122809139956</v>
       </c>
       <c r="K4" t="n">
         <v>1544.487243076824</v>
@@ -4506,25 +4506,25 @@
         <v>33.68</v>
       </c>
       <c r="S4" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T4" t="n">
-        <v>221.7556791588049</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="U4" t="n">
-        <v>468.3068717970915</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="V4" t="n">
-        <v>468.3068717970915</v>
+        <v>269.7516479801191</v>
       </c>
       <c r="W4" t="n">
-        <v>468.3068717970915</v>
+        <v>441.6425662397965</v>
       </c>
       <c r="X4" t="n">
-        <v>619.337662821285</v>
+        <v>592.6733572639899</v>
       </c>
       <c r="Y4" t="n">
-        <v>619.337662821285</v>
+        <v>704.0826579430222</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>285.4463380542246</v>
+        <v>115.3301851396645</v>
       </c>
       <c r="C5" t="n">
-        <v>235.472016596655</v>
+        <v>65.35586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>225.028424940241</v>
+        <v>54.91227202568093</v>
       </c>
       <c r="E5" t="n">
-        <v>220.6210617009798</v>
+        <v>50.50490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>215.6820428039981</v>
+        <v>45.565889889438</v>
       </c>
       <c r="G5" t="n">
-        <v>211.8867172615575</v>
+        <v>41.77056434699738</v>
       </c>
       <c r="H5" t="n">
         <v>33.68</v>
@@ -4558,25 +4558,25 @@
         <v>33.68</v>
       </c>
       <c r="J5" t="n">
-        <v>424.9891130376557</v>
+        <v>33.68</v>
       </c>
       <c r="K5" t="n">
-        <v>841.7791130376557</v>
+        <v>450.47</v>
       </c>
       <c r="L5" t="n">
-        <v>841.7791130376557</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>1258.569113037656</v>
+        <v>850.4200000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>1258.569113037656</v>
+        <v>1267.21</v>
       </c>
       <c r="O5" t="n">
-        <v>1267.21</v>
+        <v>1684</v>
       </c>
       <c r="P5" t="n">
-        <v>1267.21</v>
+        <v>1684</v>
       </c>
       <c r="Q5" t="n">
         <v>1684</v>
@@ -4603,7 +4603,7 @@
         <v>480.7157780929932</v>
       </c>
       <c r="Y5" t="n">
-        <v>368.2739268982392</v>
+        <v>198.1577739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4613,19 +4613,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>507.5171386800518</v>
+        <v>33.68</v>
       </c>
       <c r="C6" t="n">
-        <v>507.5171386800518</v>
+        <v>33.68</v>
       </c>
       <c r="D6" t="n">
-        <v>362.7098342171994</v>
+        <v>33.68</v>
       </c>
       <c r="E6" t="n">
-        <v>362.7098342171994</v>
+        <v>33.68</v>
       </c>
       <c r="F6" t="n">
-        <v>362.7098342171994</v>
+        <v>33.68</v>
       </c>
       <c r="G6" t="n">
         <v>33.68</v>
@@ -4658,31 +4658,31 @@
         <v>1189.112420368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1189.112420368536</v>
+        <v>1014.284879873102</v>
       </c>
       <c r="R6" t="n">
-        <v>1040.351008962092</v>
+        <v>865.523468466658</v>
       </c>
       <c r="S6" t="n">
-        <v>973.1146453614743</v>
+        <v>798.2871048660405</v>
       </c>
       <c r="T6" t="n">
-        <v>967.7027613033796</v>
+        <v>388.8348167675417</v>
       </c>
       <c r="U6" t="n">
-        <v>967.4902766971303</v>
+        <v>388.6223321612924</v>
       </c>
       <c r="V6" t="n">
-        <v>952.8330371097362</v>
+        <v>373.9650925738983</v>
       </c>
       <c r="W6" t="n">
-        <v>527.5805118572109</v>
+        <v>53.74337317715914</v>
       </c>
       <c r="X6" t="n">
-        <v>507.5171386800518</v>
+        <v>33.68</v>
       </c>
       <c r="Y6" t="n">
-        <v>507.5171386800518</v>
+        <v>33.68</v>
       </c>
     </row>
     <row r="7">
@@ -4692,28 +4692,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>712.5390043374616</v>
+        <v>280.2311926382866</v>
       </c>
       <c r="C7" t="n">
-        <v>712.5390043374616</v>
+        <v>297.8349901687254</v>
       </c>
       <c r="D7" t="n">
-        <v>712.5390043374616</v>
+        <v>411.1541342937255</v>
       </c>
       <c r="E7" t="n">
-        <v>830.3679085488747</v>
+        <v>528.9830385051386</v>
       </c>
       <c r="F7" t="n">
-        <v>830.3679085488747</v>
+        <v>528.9830385051386</v>
       </c>
       <c r="G7" t="n">
-        <v>983.7744744357599</v>
+        <v>682.3896043920238</v>
       </c>
       <c r="H7" t="n">
-        <v>1153.291059595158</v>
+        <v>851.9061895514213</v>
       </c>
       <c r="I7" t="n">
-        <v>1374.423938531241</v>
+        <v>1073.039068487504</v>
       </c>
       <c r="J7" t="n">
         <v>1434.122809139956</v>
@@ -4743,25 +4743,25 @@
         <v>33.68</v>
       </c>
       <c r="S7" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="T7" t="n">
-        <v>70.93025509417312</v>
+        <v>33.68</v>
       </c>
       <c r="U7" t="n">
-        <v>317.4814477324597</v>
+        <v>280.2311926382866</v>
       </c>
       <c r="V7" t="n">
-        <v>317.4814477324597</v>
+        <v>280.2311926382866</v>
       </c>
       <c r="W7" t="n">
-        <v>489.3723659921371</v>
+        <v>280.2311926382866</v>
       </c>
       <c r="X7" t="n">
-        <v>489.3723659921371</v>
+        <v>280.2311926382866</v>
       </c>
       <c r="Y7" t="n">
-        <v>600.7816666711694</v>
+        <v>280.2311926382866</v>
       </c>
     </row>
     <row r="8">
@@ -4774,19 +4774,19 @@
         <v>285.4463380542246</v>
       </c>
       <c r="C8" t="n">
-        <v>235.472016596655</v>
+        <v>65.35586368209485</v>
       </c>
       <c r="D8" t="n">
-        <v>225.028424940241</v>
+        <v>54.91227202568093</v>
       </c>
       <c r="E8" t="n">
-        <v>220.6210617009798</v>
+        <v>50.50490878641967</v>
       </c>
       <c r="F8" t="n">
-        <v>215.6820428039981</v>
+        <v>45.565889889438</v>
       </c>
       <c r="G8" t="n">
-        <v>211.8867172615575</v>
+        <v>41.77056434699738</v>
       </c>
       <c r="H8" t="n">
         <v>33.68</v>
@@ -4801,13 +4801,13 @@
         <v>424.9891130376557</v>
       </c>
       <c r="L8" t="n">
-        <v>841.7791130376557</v>
+        <v>424.9891130376557</v>
       </c>
       <c r="M8" t="n">
+        <v>841.7791130376559</v>
+      </c>
+      <c r="N8" t="n">
         <v>1258.569113037656</v>
-      </c>
-      <c r="N8" t="n">
-        <v>1675.359113037656</v>
       </c>
       <c r="O8" t="n">
         <v>1675.359113037656</v>
@@ -4859,13 +4859,13 @@
         <v>900.0695195792149</v>
       </c>
       <c r="E9" t="n">
-        <v>900.0695195792149</v>
+        <v>705.7767456696004</v>
       </c>
       <c r="F9" t="n">
-        <v>557.002608126814</v>
+        <v>362.7098342171994</v>
       </c>
       <c r="G9" t="n">
-        <v>227.9727739096147</v>
+        <v>33.68</v>
       </c>
       <c r="H9" t="n">
         <v>33.68</v>
@@ -4929,28 +4929,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>778.5375653620698</v>
+        <v>505.2612650570763</v>
       </c>
       <c r="C10" t="n">
-        <v>904.5395711805056</v>
+        <v>631.263270875512</v>
       </c>
       <c r="D10" t="n">
-        <v>948.6780958955687</v>
+        <v>744.5824150005121</v>
       </c>
       <c r="E10" t="n">
-        <v>948.6780958955687</v>
+        <v>862.4113192119252</v>
       </c>
       <c r="F10" t="n">
-        <v>1073.039068487504</v>
+        <v>986.7722918038606</v>
       </c>
       <c r="G10" t="n">
-        <v>1073.039068487504</v>
+        <v>1140.178857690746</v>
       </c>
       <c r="H10" t="n">
-        <v>1073.039068487504</v>
+        <v>1140.178857690746</v>
       </c>
       <c r="I10" t="n">
-        <v>1073.039068487504</v>
+        <v>1361.311736626829</v>
       </c>
       <c r="J10" t="n">
         <v>1434.122809139956</v>
@@ -4980,25 +4980,25 @@
         <v>33.68</v>
       </c>
       <c r="S10" t="n">
-        <v>33.68</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="T10" t="n">
-        <v>221.7556791588049</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="U10" t="n">
-        <v>468.3068717970915</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="V10" t="n">
-        <v>667.1282646830375</v>
+        <v>70.93025509417312</v>
       </c>
       <c r="W10" t="n">
-        <v>667.1282646830375</v>
+        <v>242.8211733538506</v>
       </c>
       <c r="X10" t="n">
-        <v>667.1282646830375</v>
+        <v>393.851964378044</v>
       </c>
       <c r="Y10" t="n">
-        <v>778.5375653620698</v>
+        <v>505.2612650570763</v>
       </c>
     </row>
     <row r="11">
@@ -5008,46 +5008,46 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C11" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D11" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E11" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F11" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G11" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I11" t="n">
         <v>44.72</v>
       </c>
       <c r="J11" t="n">
-        <v>137.1709049473328</v>
+        <v>44.72</v>
       </c>
       <c r="K11" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="L11" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="M11" t="n">
+        <v>137.1709049473327</v>
+      </c>
+      <c r="N11" t="n">
         <v>690.5809049473327</v>
       </c>
-      <c r="L11" t="n">
+      <c r="O11" t="n">
         <v>1243.990904947333</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1243.990904947333</v>
-      </c>
-      <c r="N11" t="n">
-        <v>1797.400904947332</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1797.400904947332</v>
       </c>
       <c r="P11" t="n">
         <v>1797.400904947332</v>
@@ -5059,25 +5059,25 @@
         <v>2236</v>
       </c>
       <c r="S11" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T11" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U11" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V11" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W11" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X11" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y11" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="12">
@@ -5087,22 +5087,22 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>472.7782575464261</v>
+        <v>119.2429040110725</v>
       </c>
       <c r="C12" t="n">
-        <v>461.5662247731743</v>
+        <v>108.0308712378207</v>
       </c>
       <c r="D12" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E12" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="F12" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="G12" t="n">
-        <v>132.5363905559749</v>
+        <v>44.72</v>
       </c>
       <c r="H12" t="n">
         <v>44.72</v>
@@ -5245,34 +5245,34 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C14" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D14" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E14" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F14" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G14" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H14" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I14" t="n">
         <v>44.72</v>
       </c>
       <c r="J14" t="n">
-        <v>436.0291130376557</v>
+        <v>64.92117127106515</v>
       </c>
       <c r="K14" t="n">
-        <v>989.4391130376558</v>
+        <v>618.3311712710652</v>
       </c>
       <c r="L14" t="n">
         <v>1171.741171271065</v>
@@ -5293,28 +5293,28 @@
         <v>2236</v>
       </c>
       <c r="R14" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S14" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T14" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U14" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V14" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W14" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X14" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y14" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="15">
@@ -5324,19 +5324,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>472.7782575464261</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C15" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D15" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E15" t="n">
-        <v>115.4327932358888</v>
+        <v>44.72</v>
       </c>
       <c r="F15" t="n">
-        <v>115.4327932358888</v>
+        <v>44.72</v>
       </c>
       <c r="G15" t="n">
         <v>44.72</v>
@@ -5372,28 +5372,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R15" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S15" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T15" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U15" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V15" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W15" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X15" t="n">
-        <v>557.5741660438614</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y15" t="n">
-        <v>507.6838703204934</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="16">
@@ -5494,37 +5494,37 @@
         <v>217.0655061454243</v>
       </c>
       <c r="F17" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G17" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H17" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I17" t="n">
         <v>44.72</v>
       </c>
       <c r="J17" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L17" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M17" t="n">
-        <v>1108.978828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N17" t="n">
-        <v>1662.388828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="O17" t="n">
-        <v>2215.798828728935</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P17" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q17" t="n">
         <v>2236</v>
@@ -5609,25 +5609,25 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R18" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S18" t="n">
-        <v>883.1445443513733</v>
+        <v>529.6091908160197</v>
       </c>
       <c r="T18" t="n">
-        <v>827.2276097882281</v>
+        <v>473.6922562528744</v>
       </c>
       <c r="U18" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V18" t="n">
-        <v>357.8124310491301</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W18" t="n">
-        <v>274.6072361907175</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X18" t="n">
-        <v>204.0388125085078</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y18" t="n">
         <v>90.8376455473191</v>
@@ -5709,7 +5709,7 @@
         <v>753.5899739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="20">
@@ -5725,43 +5725,43 @@
         <v>332.9265620512004</v>
       </c>
       <c r="D20" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E20" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F20" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G20" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H20" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I20" t="n">
         <v>44.72</v>
       </c>
       <c r="J20" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K20" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L20" t="n">
-        <v>989.4391130376558</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="M20" t="n">
-        <v>1500.287941766591</v>
+        <v>690.5809049473327</v>
       </c>
       <c r="N20" t="n">
-        <v>1682.59</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="O20" t="n">
-        <v>2236</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="P20" t="n">
-        <v>2236</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q20" t="n">
         <v>2236</v>
@@ -5798,22 +5798,22 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>391.4553531635761</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C21" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="D21" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="E21" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="F21" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="G21" t="n">
-        <v>380.2433203903244</v>
+        <v>44.72</v>
       </c>
       <c r="H21" t="n">
         <v>44.72</v>
@@ -5846,28 +5846,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R21" t="n">
-        <v>1000.885958457041</v>
+        <v>647.3506049216877</v>
       </c>
       <c r="S21" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T21" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U21" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V21" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W21" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X21" t="n">
-        <v>476.2512616610114</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y21" t="n">
-        <v>426.3609659376434</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="22">
@@ -5877,28 +5877,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C22" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D22" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E22" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F22" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G22" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H22" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I22" t="n">
-        <v>1549.112886369176</v>
+        <v>1556.823669041383</v>
       </c>
       <c r="J22" t="n">
         <v>1860.696627021627</v>
@@ -5995,28 +5995,28 @@
         <v>1500.287941766591</v>
       </c>
       <c r="O23" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P23" t="n">
-        <v>2053.697941766591</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>2236</v>
       </c>
       <c r="R23" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S23" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T23" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U23" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V23" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W23" t="n">
         <v>970.4091539265823</v>
@@ -6086,25 +6086,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S24" t="n">
-        <v>819.8336731135527</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T24" t="n">
-        <v>410.3813850150538</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U24" t="n">
-        <v>359.6638499037541</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V24" t="n">
-        <v>294.5015598113094</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W24" t="n">
-        <v>211.2963649528968</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X24" t="n">
-        <v>140.7279412706871</v>
+        <v>494.2632948060407</v>
       </c>
       <c r="Y24" t="n">
-        <v>90.8376455473191</v>
+        <v>444.3729990826727</v>
       </c>
     </row>
     <row r="25">
@@ -6168,13 +6168,13 @@
         <v>44.72</v>
       </c>
       <c r="T25" t="n">
-        <v>183.2956791588049</v>
+        <v>175.5848964865977</v>
       </c>
       <c r="U25" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V25" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W25" t="n">
         <v>644.3484002705077</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C26" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D26" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E26" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F26" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G26" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H26" t="n">
         <v>44.72</v>
@@ -6217,25 +6217,25 @@
         <v>44.72</v>
       </c>
       <c r="J26" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K26" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L26" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="M26" t="n">
-        <v>1108.978828728935</v>
+        <v>1500.287941766591</v>
       </c>
       <c r="N26" t="n">
-        <v>1662.388828728935</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="O26" t="n">
-        <v>1797.400904947332</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="P26" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q26" t="n">
         <v>2236</v>
@@ -6244,25 +6244,25 @@
         <v>2236</v>
       </c>
       <c r="S26" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T26" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U26" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V26" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W26" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X26" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y26" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1443.231821392295</v>
+        <v>275.2516144816847</v>
       </c>
       <c r="C27" t="n">
-        <v>1432.019788619043</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D27" t="n">
-        <v>1080.567579631464</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E27" t="n">
-        <v>1080.567579631464</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F27" t="n">
-        <v>1080.567579631464</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G27" t="n">
-        <v>1080.567579631464</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H27" t="n">
-        <v>1080.567579631464</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I27" t="n">
-        <v>1080.567579631464</v>
+        <v>44.72</v>
       </c>
       <c r="J27" t="n">
-        <v>1204.524099806763</v>
+        <v>168.6765201752989</v>
       </c>
       <c r="K27" t="n">
-        <v>1393.716915901147</v>
+        <v>357.8693362696823</v>
       </c>
       <c r="L27" t="n">
-        <v>1665.067377496347</v>
+        <v>629.2197978648824</v>
       </c>
       <c r="M27" t="n">
-        <v>1751.147919239206</v>
+        <v>715.3003396077416</v>
       </c>
       <c r="N27" t="n">
-        <v>1884.428203846775</v>
+        <v>848.58062421531</v>
       </c>
       <c r="O27" t="n">
-        <v>2123.470655530493</v>
+        <v>1087.623075899029</v>
       </c>
       <c r="P27" t="n">
-        <v>2236</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2236</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R27" t="n">
-        <v>2036.733538088506</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S27" t="n">
-        <v>1918.992123982838</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T27" t="n">
-        <v>1863.075189419693</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U27" t="n">
-        <v>1812.357654308393</v>
+        <v>578.9834316121869</v>
       </c>
       <c r="V27" t="n">
-        <v>1747.195364215948</v>
+        <v>513.8211415197422</v>
       </c>
       <c r="W27" t="n">
-        <v>1663.990169357536</v>
+        <v>430.6159466613296</v>
       </c>
       <c r="X27" t="n">
-        <v>1593.421745675326</v>
+        <v>360.0475229791199</v>
       </c>
       <c r="Y27" t="n">
-        <v>1543.531449951958</v>
+        <v>310.1572272557519</v>
       </c>
     </row>
     <row r="28">
@@ -6457,19 +6457,19 @@
         <v>44.72</v>
       </c>
       <c r="K29" t="n">
-        <v>598.13</v>
+        <v>44.72</v>
       </c>
       <c r="L29" t="n">
-        <v>1151.54</v>
+        <v>64.9211712710653</v>
       </c>
       <c r="M29" t="n">
-        <v>1662.388828728935</v>
+        <v>575.7700000000003</v>
       </c>
       <c r="N29" t="n">
-        <v>2215.798828728935</v>
+        <v>1129.18</v>
       </c>
       <c r="O29" t="n">
-        <v>2236</v>
+        <v>1682.59</v>
       </c>
       <c r="P29" t="n">
         <v>2236</v>
@@ -6515,19 +6515,19 @@
         <v>461.5662247731743</v>
       </c>
       <c r="D30" t="n">
-        <v>110.1140157855959</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E30" t="n">
-        <v>110.1140157855959</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="G30" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="H30" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I30" t="n">
         <v>44.72</v>
@@ -6673,16 +6673,16 @@
         <v>332.9265620512004</v>
       </c>
       <c r="D32" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E32" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F32" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G32" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H32" t="n">
         <v>44.72</v>
@@ -6691,25 +6691,25 @@
         <v>44.72</v>
       </c>
       <c r="J32" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="L32" t="n">
-        <v>598.13</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="M32" t="n">
-        <v>1108.978828728935</v>
+        <v>946.8779417665908</v>
       </c>
       <c r="N32" t="n">
-        <v>1662.388828728935</v>
+        <v>1129.18</v>
       </c>
       <c r="O32" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="P32" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q32" t="n">
         <v>2236</v>
@@ -6746,25 +6746,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>55.93203277325181</v>
+        <v>275.2516144816847</v>
       </c>
       <c r="C33" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D33" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E33" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F33" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G33" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H33" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I33" t="n">
         <v>44.72</v>
@@ -6791,31 +6791,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>1025.324879873102</v>
+        <v>1200.152420368536</v>
       </c>
       <c r="R33" t="n">
-        <v>826.0584179616072</v>
+        <v>1000.885958457041</v>
       </c>
       <c r="S33" t="n">
-        <v>708.3170038559392</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T33" t="n">
-        <v>652.400069292794</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U33" t="n">
-        <v>601.6825341814942</v>
+        <v>776.5100746769283</v>
       </c>
       <c r="V33" t="n">
-        <v>536.5202440890496</v>
+        <v>711.3477845844836</v>
       </c>
       <c r="W33" t="n">
-        <v>453.3150492306369</v>
+        <v>628.142589726071</v>
       </c>
       <c r="X33" t="n">
-        <v>382.7466255484273</v>
+        <v>557.5741660438614</v>
       </c>
       <c r="Y33" t="n">
-        <v>90.8376455473191</v>
+        <v>310.1572272557519</v>
       </c>
     </row>
     <row r="34">
@@ -6825,16 +6825,16 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C34" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D34" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E34" t="n">
-        <v>1086.406666467082</v>
+        <v>1078.695883794875</v>
       </c>
       <c r="F34" t="n">
         <v>1153.55685638681</v>
@@ -6882,19 +6882,19 @@
         <v>183.2956791588049</v>
       </c>
       <c r="U34" t="n">
-        <v>380.3468717970915</v>
+        <v>372.6360891248843</v>
       </c>
       <c r="V34" t="n">
-        <v>529.6682646830375</v>
+        <v>521.9574820108303</v>
       </c>
       <c r="W34" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X34" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y34" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="35">
@@ -6937,16 +6937,16 @@
         <v>1542.849113037656</v>
       </c>
       <c r="M35" t="n">
-        <v>1797.400904947332</v>
+        <v>1682.59</v>
       </c>
       <c r="N35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="O35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="P35" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q35" t="n">
         <v>2236</v>
@@ -6983,10 +6983,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>472.7782575464261</v>
+        <v>275.2516144816847</v>
       </c>
       <c r="C36" t="n">
-        <v>461.5662247731743</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D36" t="n">
         <v>264.0395817084329</v>
@@ -7028,31 +7028,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q36" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R36" t="n">
-        <v>1000.885958457041</v>
+        <v>803.3593153922999</v>
       </c>
       <c r="S36" t="n">
-        <v>883.1445443513733</v>
+        <v>685.6179012866319</v>
       </c>
       <c r="T36" t="n">
-        <v>827.2276097882281</v>
+        <v>629.7009667234867</v>
       </c>
       <c r="U36" t="n">
-        <v>776.5100746769283</v>
+        <v>578.9834316121869</v>
       </c>
       <c r="V36" t="n">
-        <v>711.3477845844836</v>
+        <v>513.8211415197422</v>
       </c>
       <c r="W36" t="n">
-        <v>628.142589726071</v>
+        <v>430.6159466613296</v>
       </c>
       <c r="X36" t="n">
-        <v>557.5741660438614</v>
+        <v>360.0475229791199</v>
       </c>
       <c r="Y36" t="n">
-        <v>507.6838703204934</v>
+        <v>310.1572272557519</v>
       </c>
     </row>
     <row r="37">
@@ -7141,25 +7141,25 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C38" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D38" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E38" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F38" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G38" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H38" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I38" t="n">
         <v>44.72</v>
@@ -7168,19 +7168,19 @@
         <v>44.72</v>
       </c>
       <c r="K38" t="n">
-        <v>44.72</v>
+        <v>179.7320762183976</v>
       </c>
       <c r="L38" t="n">
-        <v>598.13</v>
+        <v>733.1420762183976</v>
       </c>
       <c r="M38" t="n">
-        <v>598.13</v>
+        <v>1243.990904947333</v>
       </c>
       <c r="N38" t="n">
-        <v>690.5809049473327</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O38" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P38" t="n">
         <v>1797.400904947332</v>
@@ -7189,28 +7189,28 @@
         <v>2236</v>
       </c>
       <c r="R38" t="n">
-        <v>2231.994554156147</v>
+        <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2085.68327354774</v>
+        <v>2089.688719391593</v>
       </c>
       <c r="T38" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U38" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V38" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W38" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X38" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y38" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="39">
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>55.93203277325181</v>
+        <v>275.2516144816847</v>
       </c>
       <c r="C39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H39" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I39" t="n">
         <v>44.72</v>
@@ -7265,31 +7265,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q39" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R39" t="n">
-        <v>1000.885958457041</v>
+        <v>826.0584179616072</v>
       </c>
       <c r="S39" t="n">
-        <v>883.1445443513733</v>
+        <v>708.3170038559392</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>652.400069292794</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>601.6825341814942</v>
       </c>
       <c r="V39" t="n">
-        <v>648.0369133466629</v>
+        <v>536.5202440890496</v>
       </c>
       <c r="W39" t="n">
-        <v>564.8317184882503</v>
+        <v>453.3150492306369</v>
       </c>
       <c r="X39" t="n">
-        <v>494.2632948060407</v>
+        <v>382.7466255484273</v>
       </c>
       <c r="Y39" t="n">
-        <v>90.8376455473191</v>
+        <v>310.1572272557519</v>
       </c>
     </row>
     <row r="40">
@@ -7314,16 +7314,16 @@
         <v>1161.267639059017</v>
       </c>
       <c r="G40" t="n">
-        <v>1265.174204945903</v>
+        <v>1257.463422273695</v>
       </c>
       <c r="H40" t="n">
-        <v>1385.1907901053</v>
+        <v>1377.480007433093</v>
       </c>
       <c r="I40" t="n">
-        <v>1556.823669041383</v>
+        <v>1549.112886369176</v>
       </c>
       <c r="J40" t="n">
-        <v>1868.407409693835</v>
+        <v>1860.696627021627</v>
       </c>
       <c r="K40" t="n">
         <v>1921.561060958496</v>
@@ -7405,19 +7405,19 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L41" t="n">
-        <v>989.4391130376558</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M41" t="n">
-        <v>1500.287941766591</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N41" t="n">
-        <v>1500.287941766591</v>
+        <v>2236</v>
       </c>
       <c r="O41" t="n">
-        <v>1682.59</v>
+        <v>2236</v>
       </c>
       <c r="P41" t="n">
         <v>2236</v>
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>402.0654643105373</v>
+        <v>55.93203277325181</v>
       </c>
       <c r="C42" t="n">
-        <v>390.8534315372855</v>
+        <v>44.72</v>
       </c>
       <c r="D42" t="n">
-        <v>390.8534315372855</v>
+        <v>44.72</v>
       </c>
       <c r="E42" t="n">
         <v>44.72</v>
@@ -7502,31 +7502,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q42" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R42" t="n">
-        <v>1000.885958457041</v>
+        <v>584.0397336838671</v>
       </c>
       <c r="S42" t="n">
-        <v>883.1445443513733</v>
+        <v>466.2983195781991</v>
       </c>
       <c r="T42" t="n">
-        <v>827.2276097882281</v>
+        <v>410.3813850150538</v>
       </c>
       <c r="U42" t="n">
-        <v>776.5100746769283</v>
+        <v>359.6638499037541</v>
       </c>
       <c r="V42" t="n">
-        <v>711.3477845844836</v>
+        <v>294.5015598113094</v>
       </c>
       <c r="W42" t="n">
-        <v>628.142589726071</v>
+        <v>211.2963649528968</v>
       </c>
       <c r="X42" t="n">
-        <v>486.8613728079725</v>
+        <v>140.7279412706871</v>
       </c>
       <c r="Y42" t="n">
-        <v>436.9710770846045</v>
+        <v>90.8376455473191</v>
       </c>
     </row>
     <row r="43">
@@ -7615,46 +7615,46 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D44" t="n">
-        <v>267.972474045883</v>
+        <v>271.977919889736</v>
       </c>
       <c r="E44" t="n">
-        <v>213.0600603015712</v>
+        <v>217.0655061454243</v>
       </c>
       <c r="F44" t="n">
-        <v>157.615990899539</v>
+        <v>161.6214367433921</v>
       </c>
       <c r="G44" t="n">
-        <v>103.3156148520479</v>
+        <v>107.3210606959009</v>
       </c>
       <c r="H44" t="n">
-        <v>44.72</v>
+        <v>48.72544584385304</v>
       </c>
       <c r="I44" t="n">
         <v>44.72</v>
       </c>
       <c r="J44" t="n">
-        <v>44.72</v>
+        <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>598.13</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L44" t="n">
-        <v>598.13</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M44" t="n">
-        <v>598.13</v>
+        <v>2053.697941766591</v>
       </c>
       <c r="N44" t="n">
-        <v>1151.54</v>
+        <v>2236</v>
       </c>
       <c r="O44" t="n">
-        <v>1682.59</v>
+        <v>2236</v>
       </c>
       <c r="P44" t="n">
         <v>2236</v>
@@ -7672,19 +7672,19 @@
         <v>1850.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>55.93203277325181</v>
+        <v>275.2516144816847</v>
       </c>
       <c r="C45" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="D45" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="F45" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="G45" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="H45" t="n">
-        <v>44.72</v>
+        <v>264.0395817084329</v>
       </c>
       <c r="I45" t="n">
         <v>44.72</v>
@@ -7739,31 +7739,31 @@
         <v>1200.152420368536</v>
       </c>
       <c r="Q45" t="n">
-        <v>1200.152420368536</v>
+        <v>1025.324879873102</v>
       </c>
       <c r="R45" t="n">
-        <v>1000.885958457041</v>
+        <v>803.3593153922999</v>
       </c>
       <c r="S45" t="n">
-        <v>883.1445443513733</v>
+        <v>685.6179012866319</v>
       </c>
       <c r="T45" t="n">
-        <v>763.9167385504073</v>
+        <v>629.7009667234867</v>
       </c>
       <c r="U45" t="n">
-        <v>713.1992034391076</v>
+        <v>578.9834316121869</v>
       </c>
       <c r="V45" t="n">
-        <v>648.0369133466629</v>
+        <v>513.8211415197422</v>
       </c>
       <c r="W45" t="n">
-        <v>564.8317184882503</v>
+        <v>430.6159466613296</v>
       </c>
       <c r="X45" t="n">
-        <v>494.2632948060407</v>
+        <v>360.0475229791199</v>
       </c>
       <c r="Y45" t="n">
-        <v>444.3729990826727</v>
+        <v>310.1572272557519</v>
       </c>
     </row>
     <row r="46">
@@ -7773,25 +7773,25 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C46" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D46" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E46" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F46" t="n">
-        <v>1153.55685638681</v>
+        <v>1161.267639059017</v>
       </c>
       <c r="G46" t="n">
-        <v>1257.463422273695</v>
+        <v>1265.174204945903</v>
       </c>
       <c r="H46" t="n">
-        <v>1377.480007433093</v>
+        <v>1385.1907901053</v>
       </c>
       <c r="I46" t="n">
         <v>1549.112886369176</v>
@@ -7830,19 +7830,19 @@
         <v>183.2956791588049</v>
       </c>
       <c r="U46" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V46" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W46" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X46" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y46" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
   </sheetData>
@@ -7964,7 +7964,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -7973,7 +7973,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>544.2621276423173</v>
+        <v>965.2621276423173</v>
       </c>
       <c r="N2" t="n">
         <v>898.2489580698352</v>
@@ -7982,10 +7982,10 @@
         <v>491.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>421.2870600406814</v>
+        <v>9.015228689513952</v>
       </c>
       <c r="Q2" t="n">
-        <v>576.8125833173845</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K5" t="n">
         <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="M5" t="n">
-        <v>965.2621276423173</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N5" t="n">
-        <v>477.2489580698352</v>
+        <v>898.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>78.97603822292498</v>
+        <v>491.2478695740924</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q5" t="n">
-        <v>593.8226843274854</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>965.2621276423173</v>
@@ -8453,7 +8453,7 @@
         <v>898.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409245</v>
+        <v>491.2478695740924</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
@@ -8675,25 +8675,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>128.4277587171436</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>544.2621276423173</v>
+        <v>637.6468801143706</v>
       </c>
       <c r="N11" t="n">
         <v>1036.248958069835</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q11" t="n">
         <v>615.8520732695737</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>55.44822975121676</v>
       </c>
       <c r="K14" t="n">
         <v>559</v>
       </c>
       <c r="L14" t="n">
-        <v>184.1434931650599</v>
+        <v>559</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -9149,10 +9149,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -9164,13 +9164,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O17" t="n">
-        <v>629.2478695740924</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P17" t="n">
-        <v>20.69228354680773</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9386,28 +9386,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
-        <v>559</v>
+        <v>93.38475247205326</v>
       </c>
       <c r="M20" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N20" t="n">
-        <v>661.3924512348951</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O20" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q20" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9638,13 +9638,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O23" t="n">
-        <v>629.2478695740924</v>
+        <v>370.3619737970638</v>
       </c>
       <c r="P23" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q23" t="n">
-        <v>356.9661774925453</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9860,13 +9860,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J26" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>559</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,13 +9875,13 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O26" t="n">
-        <v>206.6237041381302</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P26" t="n">
-        <v>0.2870600406814136</v>
+        <v>184.4305532057413</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,10 +10100,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>559.0000000000001</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,10 +10112,10 @@
         <v>1036.248958069835</v>
       </c>
       <c r="O29" t="n">
-        <v>90.65309308021877</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q29" t="n">
         <v>172.8226843274854</v>
@@ -10334,28 +10334,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J32" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>1036.248958069835</v>
+        <v>661.3924512348954</v>
       </c>
       <c r="O32" t="n">
-        <v>206.6237041381302</v>
+        <v>629.2478695740924</v>
       </c>
       <c r="P32" t="n">
-        <v>0.2870600406814136</v>
+        <v>559.2870600406815</v>
       </c>
       <c r="Q32" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10580,10 +10580,10 @@
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>801.3851497733039</v>
+        <v>685.4145387153924</v>
       </c>
       <c r="N35" t="n">
-        <v>477.2489580698352</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O35" t="n">
         <v>70.24786957409245</v>
@@ -10592,7 +10592,7 @@
         <v>0.2870600406814136</v>
       </c>
       <c r="Q35" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,22 +10811,22 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N38" t="n">
-        <v>570.6337105418884</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>629.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P38" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11048,7 +11048,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
         <v>559</v>
@@ -11057,13 +11057,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>661.3924512348951</v>
       </c>
       <c r="O41" t="n">
-        <v>254.3913627391524</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>172.8226843274854</v>
@@ -11282,25 +11282,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>661.3924512348951</v>
       </c>
       <c r="O44" t="n">
-        <v>606.6620109882341</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>172.8226843274854</v>
@@ -26290,13 +26290,13 @@
         <v>1542736.874407429</v>
       </c>
       <c r="I2" t="n">
-        <v>1542736.874407429</v>
+        <v>1542736.874407428</v>
       </c>
       <c r="J2" t="n">
         <v>1542736.874407429</v>
       </c>
       <c r="K2" t="n">
-        <v>1542736.874407428</v>
+        <v>1542736.874407429</v>
       </c>
       <c r="L2" t="n">
         <v>1542736.874407429</v>
@@ -26308,7 +26308,7 @@
         <v>1542736.874407429</v>
       </c>
       <c r="O2" t="n">
-        <v>1542736.874407428</v>
+        <v>1542736.874407429</v>
       </c>
       <c r="P2" t="n">
         <v>1542736.874407429</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>566354.9592425094</v>
+        <v>567917.5723359546</v>
       </c>
       <c r="C4" t="n">
-        <v>564322.4434789647</v>
+        <v>565885.0565724098</v>
       </c>
       <c r="D4" t="n">
-        <v>562287.1704809261</v>
+        <v>563849.7835743712</v>
       </c>
       <c r="E4" t="n">
-        <v>543094.0532265352</v>
+        <v>544835.9030396428</v>
       </c>
       <c r="F4" t="n">
-        <v>541151.157881031</v>
+        <v>542893.0076941388</v>
       </c>
       <c r="G4" t="n">
-        <v>539205.5814128455</v>
+        <v>540947.4312259532</v>
       </c>
       <c r="H4" t="n">
-        <v>537257.3045955442</v>
+        <v>538999.1544086519</v>
       </c>
       <c r="I4" t="n">
-        <v>535306.307952184</v>
+        <v>537048.1577652916</v>
       </c>
       <c r="J4" t="n">
-        <v>533352.5717505589</v>
+        <v>535094.4215636665</v>
       </c>
       <c r="K4" t="n">
-        <v>531396.0759983395</v>
+        <v>533137.9258114471</v>
       </c>
       <c r="L4" t="n">
-        <v>529436.8004380801</v>
+        <v>531178.6502511877</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421008</v>
+        <v>529216.5743552084</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072472</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495091</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984991</v>
+        <v>523313.3352116067</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>768965.5151649193</v>
+        <v>767402.9020714746</v>
       </c>
       <c r="C6" t="n">
-        <v>919190.0309284643</v>
+        <v>917627.4178350192</v>
       </c>
       <c r="D6" t="n">
-        <v>921225.3039265027</v>
+        <v>919662.6908330575</v>
       </c>
       <c r="E6" t="n">
-        <v>607655.4711808938</v>
+        <v>605913.6213677862</v>
       </c>
       <c r="F6" t="n">
-        <v>938174.3665263975</v>
+        <v>936432.51671329</v>
       </c>
       <c r="G6" t="n">
-        <v>940119.9429945833</v>
+        <v>938378.0931814756</v>
       </c>
       <c r="H6" t="n">
-        <v>942068.2198118843</v>
+        <v>940326.3699987772</v>
       </c>
       <c r="I6" t="n">
-        <v>944019.2164552446</v>
+        <v>942277.3666421367</v>
       </c>
       <c r="J6" t="n">
-        <v>517780.9526568701</v>
+        <v>516039.1028437623</v>
       </c>
       <c r="K6" t="n">
-        <v>947929.4484090889</v>
+        <v>946187.5985959815</v>
       </c>
       <c r="L6" t="n">
-        <v>949888.7239693489</v>
+        <v>948146.8741562413</v>
       </c>
       <c r="M6" t="n">
-        <v>903274.7998653282</v>
+        <v>901532.9500522201</v>
       </c>
       <c r="N6" t="n">
-        <v>953815.6969001818</v>
+        <v>952073.8470870741</v>
       </c>
       <c r="O6" t="n">
-        <v>675783.4361579192</v>
+        <v>674041.5863448117</v>
       </c>
       <c r="P6" t="n">
-        <v>957754.03900893</v>
+        <v>956012.1891958219</v>
       </c>
     </row>
   </sheetData>
@@ -26999,10 +26999,10 @@
         <v>350</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>-0</v>
@@ -27024,22 +27024,22 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C3" t="n">
         <v>-0</v>
       </c>
-      <c r="C3" t="n">
-        <v>0</v>
-      </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
@@ -27112,7 +27112,7 @@
         <v>138</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O4" t="n">
         <v>-0</v>
@@ -27451,10 +27451,10 @@
         <v>400</v>
       </c>
       <c r="H2" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>232.5447671255646</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27518,22 +27518,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
-        <v>280.4177134961084</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E3" t="n">
-        <v>342.6720972219126</v>
+        <v>150.3222510513942</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27572,7 +27572,7 @@
         <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27597,10 +27597,10 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D4" t="n">
-        <v>342.8211263854157</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>339.2430722787975</v>
       </c>
       <c r="F4" t="n">
         <v>400</v>
@@ -27609,16 +27609,16 @@
         <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
         <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
+        <v>35.26894883590776</v>
+      </c>
+      <c r="K4" t="n">
         <v>400</v>
-      </c>
-      <c r="K4" t="n">
-        <v>288.520773801143</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T4" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U4" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V4" t="n">
         <v>400</v>
       </c>
-      <c r="U4" t="n">
+      <c r="W4" t="n">
         <v>400</v>
-      </c>
-      <c r="V4" t="n">
-        <v>199.1703102162162</v>
-      </c>
-      <c r="W4" t="n">
-        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
       </c>
       <c r="Y4" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5">
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>231.5850086145855</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
@@ -27739,7 +27739,7 @@
         <v>400</v>
       </c>
       <c r="Y5" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
     </row>
     <row r="6">
@@ -27755,7 +27755,7 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>204.5784554794787</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
@@ -27764,7 +27764,7 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
         <v>332.1680871864211</v>
@@ -27794,7 +27794,7 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>400</v>
@@ -27803,7 +27803,7 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27812,7 +27812,7 @@
         <v>400</v>
       </c>
       <c r="W6" t="n">
-        <v>11.37314290982852</v>
+        <v>115.3536407070567</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27828,13 +27828,13 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>287.1138003370787</v>
+      </c>
+      <c r="C7" t="n">
+        <v>290.5068603151545</v>
+      </c>
+      <c r="D7" t="n">
         <v>400</v>
-      </c>
-      <c r="C7" t="n">
-        <v>272.7252466480447</v>
-      </c>
-      <c r="D7" t="n">
-        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
         <v>400</v>
@@ -27852,7 +27852,7 @@
         <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>95.57083833966027</v>
+        <v>400</v>
       </c>
       <c r="K7" t="n">
         <v>400</v>
@@ -27879,7 +27879,7 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>400</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T7" t="n">
         <v>210.0245665062577</v>
@@ -27891,13 +27891,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27910,7 +27910,7 @@
         <v>400</v>
       </c>
       <c r="C8" t="n">
-        <v>400</v>
+        <v>231.5850086145855</v>
       </c>
       <c r="D8" t="n">
         <v>400</v>
@@ -27925,7 +27925,7 @@
         <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>231.5850086145855</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -27995,7 +27995,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>150.3222510513942</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -28004,7 +28004,7 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>139.8182410159026</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
         <v>217.1263858913485</v>
@@ -28071,25 +28071,25 @@
         <v>400</v>
       </c>
       <c r="D10" t="n">
-        <v>330.1205864546091</v>
+        <v>400</v>
       </c>
       <c r="E10" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F10" t="n">
         <v>400</v>
       </c>
       <c r="G10" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H10" t="n">
         <v>228.7711261016186</v>
       </c>
       <c r="I10" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>400</v>
+        <v>108.8154867279549</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28116,22 +28116,22 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
+        <v>210.0245665062577</v>
+      </c>
+      <c r="U10" t="n">
+        <v>150.9583912744579</v>
+      </c>
+      <c r="V10" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W10" t="n">
         <v>400</v>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>400</v>
-      </c>
-      <c r="V10" t="n">
-        <v>400</v>
-      </c>
-      <c r="W10" t="n">
-        <v>226.3728098387097</v>
-      </c>
-      <c r="X10" t="n">
-        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
         <v>400</v>
@@ -28165,7 +28165,7 @@
         <v>350</v>
       </c>
       <c r="I11" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -28195,7 +28195,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T11" t="n">
         <v>350</v>
@@ -28223,13 +28223,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
         <v>350</v>
       </c>
       <c r="D12" t="n">
-        <v>347.9376868977026</v>
+        <v>285.2599243722601</v>
       </c>
       <c r="E12" t="n">
         <v>342.6720972219126</v>
@@ -28238,10 +28238,10 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H12" t="n">
-        <v>245.2298605360059</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I12" t="n">
         <v>217.1263858913485</v>
@@ -28402,7 +28402,7 @@
         <v>350</v>
       </c>
       <c r="I14" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28429,7 +28429,7 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S14" t="n">
         <v>350</v>
@@ -28469,13 +28469,13 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F15" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G15" t="n">
-        <v>255.7338705714974</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H15" t="n">
         <v>332.1680871864211</v>
@@ -28508,10 +28508,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T15" t="n">
         <v>350</v>
@@ -28630,7 +28630,7 @@
         <v>350</v>
       </c>
       <c r="F17" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="G17" t="n">
         <v>350</v>
@@ -28639,7 +28639,7 @@
         <v>350</v>
       </c>
       <c r="I17" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28745,7 +28745,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
         <v>350</v>
@@ -28754,10 +28754,10 @@
         <v>350</v>
       </c>
       <c r="U18" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="W18" t="n">
         <v>350</v>
@@ -28766,7 +28766,7 @@
         <v>350</v>
       </c>
       <c r="Y18" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
     </row>
     <row r="19">
@@ -28776,76 +28776,76 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>350</v>
+      </c>
+      <c r="C19" t="n">
+        <v>350</v>
+      </c>
+      <c r="D19" t="n">
+        <v>350</v>
+      </c>
+      <c r="E19" t="n">
+        <v>350</v>
+      </c>
+      <c r="F19" t="n">
+        <v>350</v>
+      </c>
+      <c r="G19" t="n">
+        <v>350</v>
+      </c>
+      <c r="H19" t="n">
+        <v>350</v>
+      </c>
+      <c r="I19" t="n">
+        <v>350</v>
+      </c>
+      <c r="J19" t="n">
+        <v>350</v>
+      </c>
+      <c r="K19" t="n">
+        <v>350</v>
+      </c>
+      <c r="L19" t="n">
+        <v>350</v>
+      </c>
+      <c r="M19" t="n">
+        <v>350</v>
+      </c>
+      <c r="N19" t="n">
+        <v>350</v>
+      </c>
+      <c r="O19" t="n">
+        <v>350</v>
+      </c>
+      <c r="P19" t="n">
+        <v>350</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>350</v>
+      </c>
+      <c r="R19" t="n">
+        <v>350</v>
+      </c>
+      <c r="S19" t="n">
+        <v>350</v>
+      </c>
+      <c r="T19" t="n">
+        <v>350</v>
+      </c>
+      <c r="U19" t="n">
+        <v>350</v>
+      </c>
+      <c r="V19" t="n">
+        <v>350</v>
+      </c>
+      <c r="W19" t="n">
+        <v>350</v>
+      </c>
+      <c r="X19" t="n">
+        <v>350</v>
+      </c>
+      <c r="Y19" t="n">
         <v>342.2113306341342</v>
-      </c>
-      <c r="C19" t="n">
-        <v>350</v>
-      </c>
-      <c r="D19" t="n">
-        <v>350</v>
-      </c>
-      <c r="E19" t="n">
-        <v>350</v>
-      </c>
-      <c r="F19" t="n">
-        <v>350</v>
-      </c>
-      <c r="G19" t="n">
-        <v>350</v>
-      </c>
-      <c r="H19" t="n">
-        <v>350</v>
-      </c>
-      <c r="I19" t="n">
-        <v>350</v>
-      </c>
-      <c r="J19" t="n">
-        <v>350</v>
-      </c>
-      <c r="K19" t="n">
-        <v>350</v>
-      </c>
-      <c r="L19" t="n">
-        <v>350</v>
-      </c>
-      <c r="M19" t="n">
-        <v>350</v>
-      </c>
-      <c r="N19" t="n">
-        <v>350</v>
-      </c>
-      <c r="O19" t="n">
-        <v>350</v>
-      </c>
-      <c r="P19" t="n">
-        <v>350</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>350</v>
-      </c>
-      <c r="R19" t="n">
-        <v>350</v>
-      </c>
-      <c r="S19" t="n">
-        <v>350</v>
-      </c>
-      <c r="T19" t="n">
-        <v>350</v>
-      </c>
-      <c r="U19" t="n">
-        <v>350</v>
-      </c>
-      <c r="V19" t="n">
-        <v>350</v>
-      </c>
-      <c r="W19" t="n">
-        <v>350</v>
-      </c>
-      <c r="X19" t="n">
-        <v>350</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>350</v>
       </c>
     </row>
     <row r="20">
@@ -28861,7 +28861,7 @@
         <v>350</v>
       </c>
       <c r="D20" t="n">
-        <v>346.0346086145855</v>
+        <v>350</v>
       </c>
       <c r="E20" t="n">
         <v>350</v>
@@ -28876,7 +28876,7 @@
         <v>350</v>
       </c>
       <c r="I20" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28952,7 +28952,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I21" t="n">
         <v>217.1263858913485</v>
@@ -28982,10 +28982,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>350</v>
+        <v>287.3222374745576</v>
       </c>
       <c r="T21" t="n">
         <v>350</v>
@@ -29000,7 +29000,7 @@
         <v>350</v>
       </c>
       <c r="X21" t="n">
-        <v>269.4903246609786</v>
+        <v>350</v>
       </c>
       <c r="Y21" t="n">
         <v>350</v>
@@ -29013,7 +29013,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="C22" t="n">
         <v>350</v>
@@ -29037,7 +29037,7 @@
         <v>350</v>
       </c>
       <c r="J22" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="K22" t="n">
         <v>350</v>
@@ -29140,7 +29140,7 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S23" t="n">
         <v>350</v>
@@ -29155,7 +29155,7 @@
         <v>350</v>
       </c>
       <c r="W23" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="X23" t="n">
         <v>350</v>
@@ -29171,7 +29171,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="C24" t="n">
         <v>350</v>
@@ -29222,10 +29222,10 @@
         <v>350</v>
       </c>
       <c r="S24" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="U24" t="n">
         <v>350</v>
@@ -29237,7 +29237,7 @@
         <v>350</v>
       </c>
       <c r="X24" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="Y24" t="n">
         <v>350</v>
@@ -29304,7 +29304,7 @@
         <v>350</v>
       </c>
       <c r="T25" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="U25" t="n">
         <v>350</v>
@@ -29313,7 +29313,7 @@
         <v>350</v>
       </c>
       <c r="W25" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="X25" t="n">
         <v>350</v>
@@ -29347,7 +29347,7 @@
         <v>350</v>
       </c>
       <c r="H26" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="I26" t="n">
         <v>150.0811596826846</v>
@@ -29380,7 +29380,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S26" t="n">
-        <v>346.0346086145856</v>
+        <v>350</v>
       </c>
       <c r="T26" t="n">
         <v>350</v>
@@ -29408,13 +29408,13 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>285.25992437226</v>
+        <v>350</v>
       </c>
       <c r="C27" t="n">
         <v>350</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E27" t="n">
         <v>342.6720972219126</v>
@@ -29429,7 +29429,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -29465,7 +29465,7 @@
         <v>350</v>
       </c>
       <c r="U27" t="n">
-        <v>350</v>
+        <v>154.448623365906</v>
       </c>
       <c r="V27" t="n">
         <v>350</v>
@@ -29651,22 +29651,22 @@
         <v>350</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E30" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>274.8961667101369</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G30" t="n">
         <v>325.7395358750273</v>
       </c>
       <c r="H30" t="n">
-        <v>332.1680871864211</v>
+        <v>136.6167105523271</v>
       </c>
       <c r="I30" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29809,19 +29809,19 @@
         <v>350</v>
       </c>
       <c r="D32" t="n">
+        <v>350</v>
+      </c>
+      <c r="E32" t="n">
+        <v>350</v>
+      </c>
+      <c r="F32" t="n">
+        <v>350</v>
+      </c>
+      <c r="G32" t="n">
+        <v>350</v>
+      </c>
+      <c r="H32" t="n">
         <v>346.0346086145855</v>
-      </c>
-      <c r="E32" t="n">
-        <v>350</v>
-      </c>
-      <c r="F32" t="n">
-        <v>350</v>
-      </c>
-      <c r="G32" t="n">
-        <v>350</v>
-      </c>
-      <c r="H32" t="n">
-        <v>350</v>
       </c>
       <c r="I32" t="n">
         <v>150.0811596826846</v>
@@ -29903,7 +29903,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I33" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29927,7 +29927,7 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R33" t="n">
         <v>350</v>
@@ -29951,7 +29951,7 @@
         <v>350</v>
       </c>
       <c r="Y33" t="n">
-        <v>110.4015025650372</v>
+        <v>154.448623365906</v>
       </c>
     </row>
     <row r="34">
@@ -29973,7 +29973,7 @@
         <v>350</v>
       </c>
       <c r="F34" t="n">
-        <v>342.2113306341341</v>
+        <v>350</v>
       </c>
       <c r="G34" t="n">
         <v>350</v>
@@ -30018,7 +30018,7 @@
         <v>350</v>
       </c>
       <c r="U34" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="V34" t="n">
         <v>350</v>
@@ -30125,7 +30125,7 @@
         <v>350</v>
       </c>
       <c r="D36" t="n">
-        <v>152.3863102636086</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
@@ -30164,10 +30164,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>350</v>
+        <v>327.5278884563857</v>
       </c>
       <c r="S36" t="n">
         <v>350</v>
@@ -30298,7 +30298,7 @@
         <v>350</v>
       </c>
       <c r="I38" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>246.9132074428799</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
         <v>350</v>
@@ -30377,7 +30377,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>350</v>
@@ -30416,7 +30416,7 @@
         <v>350</v>
       </c>
       <c r="V39" t="n">
-        <v>287.3222374745574</v>
+        <v>350</v>
       </c>
       <c r="W39" t="n">
         <v>350</v>
@@ -30425,7 +30425,7 @@
         <v>350</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>327.5278884563858</v>
       </c>
     </row>
     <row r="40">
@@ -30450,7 +30450,7 @@
         <v>350</v>
       </c>
       <c r="G40" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="H40" t="n">
         <v>350</v>
@@ -30462,7 +30462,7 @@
         <v>350</v>
       </c>
       <c r="K40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="L40" t="n">
         <v>350</v>
@@ -30602,7 +30602,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E42" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F42" t="n">
         <v>339.6362423378769</v>
@@ -30638,10 +30638,10 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>350</v>
+        <v>110.4015025650372</v>
       </c>
       <c r="S42" t="n">
         <v>350</v>
@@ -30659,7 +30659,7 @@
         <v>350</v>
       </c>
       <c r="X42" t="n">
-        <v>279.99433469647</v>
+        <v>350</v>
       </c>
       <c r="Y42" t="n">
         <v>350</v>
@@ -30772,7 +30772,7 @@
         <v>350</v>
       </c>
       <c r="I44" t="n">
-        <v>150.0811596826846</v>
+        <v>146.1157682972701</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -30808,7 +30808,7 @@
         <v>350</v>
       </c>
       <c r="U44" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="V44" t="n">
         <v>350</v>
@@ -30830,7 +30830,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="C45" t="n">
         <v>350</v>
@@ -30851,7 +30851,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -30875,16 +30875,16 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>350</v>
+        <v>327.5278884563857</v>
       </c>
       <c r="S45" t="n">
         <v>350</v>
       </c>
       <c r="T45" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="U45" t="n">
         <v>350</v>
@@ -30930,7 +30930,7 @@
         <v>350</v>
       </c>
       <c r="I46" t="n">
-        <v>350</v>
+        <v>342.2113306341342</v>
       </c>
       <c r="J46" t="n">
         <v>350</v>
@@ -30966,7 +30966,7 @@
         <v>350</v>
       </c>
       <c r="U46" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="V46" t="n">
         <v>350</v>
@@ -34743,7 +34743,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -34752,7 +34752,7 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="N2" t="n">
         <v>421</v>
@@ -34761,10 +34761,10 @@
         <v>421</v>
       </c>
       <c r="P2" t="n">
-        <v>421</v>
+        <v>8.728168648832536</v>
       </c>
       <c r="Q2" t="n">
-        <v>403.989898989899</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34883,10 +34883,10 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>57.28490832986018</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>58.26216744184091</v>
       </c>
       <c r="F4" t="n">
         <v>125.6171440322581</v>
@@ -34895,16 +34895,16 @@
         <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>364.7310511640923</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T4" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="5">
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
         <v>421</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>403.9898989898991</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
         <v>421</v>
       </c>
-      <c r="N5" t="n">
-        <v>0</v>
-      </c>
       <c r="O5" t="n">
-        <v>8.728168648832536</v>
+        <v>421</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35114,13 +35114,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>17.78161366710988</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
         <v>119.0190951630435</v>
@@ -35138,7 +35138,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>60.3018895037525</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K7" t="n">
         <v>111.479226198857</v>
@@ -35165,7 +35165,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>37.62652029714457</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -35177,13 +35177,13 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35223,7 +35223,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>421</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
         <v>421</v>
@@ -35232,7 +35232,7 @@
         <v>421</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>421</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -35357,25 +35357,25 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D10" t="n">
-        <v>44.58436839905365</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F10" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>364.7310511640923</v>
+        <v>73.54653789204711</v>
       </c>
       <c r="K10" t="n">
         <v>111.479226198857</v>
@@ -35402,22 +35402,22 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
-        <v>189.9754334937423</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
         <v>112.5346471505376</v>
@@ -35454,25 +35454,25 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>93.38475247205329</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>93.38475247205324</v>
       </c>
       <c r="N11" t="n">
         <v>559</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q11" t="n">
         <v>443.0293889420883</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>20.40522350612643</v>
       </c>
       <c r="K14" t="n">
         <v>559</v>
       </c>
       <c r="L14" t="n">
-        <v>184.1434931650599</v>
+        <v>559</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35928,10 +35928,10 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -35943,13 +35943,13 @@
         <v>559</v>
       </c>
       <c r="O17" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P17" t="n">
-        <v>20.40522350612631</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36062,7 +36062,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>55.09753029705556</v>
+        <v>62.88619966292134</v>
       </c>
       <c r="C19" t="n">
         <v>77.27475335195533</v>
@@ -36131,7 +36131,7 @@
         <v>102.5563545698924</v>
       </c>
       <c r="Y19" t="n">
-        <v>62.53464715053764</v>
+        <v>54.74597778467183</v>
       </c>
     </row>
     <row r="20">
@@ -36165,28 +36165,28 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L20" t="n">
+        <v>93.38475247205326</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
         <v>559</v>
       </c>
-      <c r="M20" t="n">
-        <v>516.0089179080152</v>
-      </c>
-      <c r="N20" t="n">
-        <v>184.1434931650599</v>
-      </c>
       <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
         <v>559</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36299,7 +36299,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>55.09753029705556</v>
+        <v>62.88619966292134</v>
       </c>
       <c r="C22" t="n">
         <v>77.27475335195533</v>
@@ -36323,7 +36323,7 @@
         <v>173.3665443798817</v>
       </c>
       <c r="J22" t="n">
-        <v>314.7310511640923</v>
+        <v>306.9423817982264</v>
       </c>
       <c r="K22" t="n">
         <v>61.47922619885696</v>
@@ -36417,13 +36417,13 @@
         <v>559</v>
       </c>
       <c r="O23" t="n">
-        <v>559</v>
+        <v>300.1141042229714</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>184.1434931650599</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36590,7 +36590,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>139.9754334937423</v>
+        <v>132.1867641278765</v>
       </c>
       <c r="U25" t="n">
         <v>199.0416087255421</v>
@@ -36599,7 +36599,7 @@
         <v>150.8296897837838</v>
       </c>
       <c r="W25" t="n">
-        <v>115.8385207954244</v>
+        <v>123.6271901612903</v>
       </c>
       <c r="X25" t="n">
         <v>102.5563545698924</v>
@@ -36639,13 +36639,13 @@
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="n">
         <v>559</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,13 +36654,13 @@
         <v>559</v>
       </c>
       <c r="O26" t="n">
-        <v>136.3758345640378</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36879,10 +36879,10 @@
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>559.0000000000001</v>
+        <v>20.40522350612657</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,10 +36891,10 @@
         <v>559</v>
       </c>
       <c r="O29" t="n">
-        <v>20.40522350612631</v>
+        <v>559</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -37113,28 +37113,28 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
+        <v>184.1434931650601</v>
+      </c>
+      <c r="O32" t="n">
         <v>559</v>
       </c>
-      <c r="O32" t="n">
-        <v>136.3758345640378</v>
-      </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="Q32" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37259,7 +37259,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F34" t="n">
-        <v>67.82847466639221</v>
+        <v>75.61714403225807</v>
       </c>
       <c r="G34" t="n">
         <v>104.95612715847</v>
@@ -37304,7 +37304,7 @@
         <v>139.9754334937423</v>
       </c>
       <c r="U34" t="n">
-        <v>199.0416087255421</v>
+        <v>191.2529393596762</v>
       </c>
       <c r="V34" t="n">
         <v>150.8296897837838</v>
@@ -37359,10 +37359,10 @@
         <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>257.1230221309866</v>
+        <v>141.1524110730751</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -37371,7 +37371,7 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
         <v>0</v>
@@ -37590,22 +37590,22 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>136.375834564038</v>
       </c>
       <c r="L38" t="n">
         <v>559</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N38" t="n">
-        <v>93.38475247205321</v>
+        <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
         <v>443.0293889420883</v>
@@ -37736,7 +37736,7 @@
         <v>75.61714403225807</v>
       </c>
       <c r="G40" t="n">
-        <v>104.95612715847</v>
+        <v>97.1674577926042</v>
       </c>
       <c r="H40" t="n">
         <v>121.2288738983814</v>
@@ -37748,7 +37748,7 @@
         <v>314.7310511640923</v>
       </c>
       <c r="K40" t="n">
-        <v>53.69055683299113</v>
+        <v>61.47922619885696</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
@@ -37827,7 +37827,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
         <v>559</v>
@@ -37836,13 +37836,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="O41" t="n">
-        <v>184.1434931650599</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -38061,25 +38061,25 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
         <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N44" t="n">
-        <v>559</v>
+        <v>184.1434931650599</v>
       </c>
       <c r="O44" t="n">
-        <v>536.4141414141416</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -38216,7 +38216,7 @@
         <v>121.2288738983814</v>
       </c>
       <c r="I46" t="n">
-        <v>173.3665443798817</v>
+        <v>165.577875014016</v>
       </c>
       <c r="J46" t="n">
         <v>314.7310511640923</v>
@@ -38252,7 +38252,7 @@
         <v>139.9754334937423</v>
       </c>
       <c r="U46" t="n">
-        <v>191.2529393596762</v>
+        <v>199.0416087255421</v>
       </c>
       <c r="V46" t="n">
         <v>150.8296897837838</v>
